--- a/data/go_japan_campaign_stress_test.xlsx
+++ b/data/go_japan_campaign_stress_test.xlsx
@@ -1764,7 +1764,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="34" t="str">
-        <x:v>Trip.com App Homepage Banner</x:v>
+        <x:v>App Homepage Banner</x:v>
       </x:c>
       <x:c r="B2" s="72" t="str">
         <x:v>All markets</x:v>
@@ -1787,7 +1787,7 @@
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="36" t="str">
-        <x:v>Trip.com App Hotel Homepage Banner</x:v>
+        <x:v>App Hotel Homepage Banner</x:v>
       </x:c>
       <x:c r="B3" s="73" t="str">
         <x:v>All markets</x:v>
@@ -1810,7 +1810,7 @@
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="36" t="str">
-        <x:v>Trip.com App Flight Homepage Banner</x:v>
+        <x:v>App Flight Homepage Banner</x:v>
       </x:c>
       <x:c r="B4" s="73" t="str">
         <x:v>All markets</x:v>
